--- a/page_passage_source/instagram_threads.xlsx
+++ b/page_passage_source/instagram_threads.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kulu/Desktop/PhD/Research/AIGC_Social_Media/dataset(organization_needed)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kulu/Desktop/PhD/Research/AIGC_Social_Media/final_dataset/page_passage_source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A06A9E-9542-6242-B02B-76403C2FABB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F1B601-7F49-9147-80A4-3AFB281521A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="500" yWindow="500" windowWidth="34560" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="500" yWindow="500" windowWidth="34560" windowHeight="19920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -93,9 +93,6 @@
 No Related Articles Write with Meta AI on Instagram How to use the paid partnership label to tag organic branded content on Instagram How to add labels to Instagram chats Get started with branded content on Instagram Instagram partnership ad specifications for creators Set audience restrictions for branded content on Instagram Related Articles Write with Meta AI on Instagram How to use the paid partnership label to tag organic branded content on Instagram How to add labels to Instagram chats Get started with branded content on Instagram Instagram partnership ad specifications for creators Set audience restrictions for branded content on Instagram About Us API Jobs Terms Privacy © 2025 Meta Feedback</t>
   </si>
   <si>
-    <t>https://help.instagram.com/231732506511219/?cms_platform=android-app&amp;helpref=platform_switcher</t>
-  </si>
-  <si>
     <t>artificial, ai, intelligen</t>
   </si>
   <si>
@@ -130,9 +127,6 @@
 No Related Articles Using stickers on Instagram Create your own stickers on Instagram with Cutouts Create or delete custom stickers with Cutouts on Instagram Add Yours sticker on Instagram Send a GIF or sticker in an Instagram chat Related Articles Using stickers on Instagram Create your own stickers on Instagram with Cutouts Create or delete custom stickers with Cutouts on Instagram Add Yours sticker on Instagram Send a GIF or sticker in an Instagram chat About Us API Jobs Terms Privacy © 2025 Meta Feedback</t>
   </si>
   <si>
-    <t>https://help.instagram.com/430610480097641/?cms_platform=android-app&amp;helpref=platform_switcher</t>
-  </si>
-  <si>
     <t>ai</t>
   </si>
   <si>
@@ -177,9 +171,6 @@
 Yes
 No Related Articles Write with Meta AI on Instagram Create a custom AI with Meta AI Studio on Instagram Use Meta AI on Instagram Delete your custom AI on Instagram Edit an image with Meta AI in chats on Instagram Edit your custom AI with Meta AI Studio on Instagram Related Articles Write with Meta AI on Instagram Create a custom AI with Meta AI Studio on Instagram Use Meta AI on Instagram Delete your custom AI on Instagram Edit an image with Meta AI in chats on Instagram Edit your custom AI with Meta AI Studio on Instagram About Us API Jobs Terms
 Privacy © 2025 Meta Feedback</t>
-  </si>
-  <si>
-    <t>https://help.instagram.com/2050445508681504/?cms_platform=iphone-app&amp;helpref=platform_switcher</t>
   </si>
   <si>
     <t>Use Meta AI on Instagram | Instagram Help Center Help Center English (US) Instagram Features Your Profile Sharing Photos and Videos Exploring Photos and Videos Messaging Send, View and Manage Messages Group Chats Audio and Video Calls Channels End-to-End Encrypted Chats Reels Edits Stories Live Fundraisers and Donations Shop Payments in Instagram Manage Your Account Staying Safe Privacy, Security and Reporting Terms and Policies Threads
@@ -471,9 +462,6 @@
 No Related Articles About Instagram Insights View account and ad insights on Instagram View channel insights on Instagram View insights on your Instagram posts Write with Meta AI on Instagram Related Articles About Instagram Insights View account and ad insights on Instagram View channel insights on Instagram View insights on your Instagram posts Write with Meta AI on Instagram About Us API Jobs Terms Privacy © 2025 Meta Feedback</t>
   </si>
   <si>
-    <t>https://help.instagram.com/1090232732886566/?cms_platform=iphone-app</t>
-  </si>
-  <si>
     <t>Expand photos with Meta AI on Instagram Stories | Instagram Help Center Help Center English (US) Instagram Features Manage Your Account Staying Safe Privacy, Security and Reporting Terms and Policies Threads Expand photos with Meta AI on Instagram Stories
 Android App Help iPhone App
 Help More Android App Help
@@ -533,6 +521,18 @@
   </si>
   <si>
     <t>passage_type</t>
+  </si>
+  <si>
+    <t>https://help.instagram.com/231732506511219</t>
+  </si>
+  <si>
+    <t>https://help.instagram.com/430610480097641</t>
+  </si>
+  <si>
+    <t>https://help.instagram.com/2050445508681504</t>
+  </si>
+  <si>
+    <t>https://help.instagram.com/1090232732886566</t>
   </si>
 </sst>
 </file>
@@ -943,25 +943,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -981,10 +981,10 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -995,19 +995,19 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -1018,19 +1018,19 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -1041,19 +1041,19 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -1064,19 +1064,19 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -1087,19 +1087,19 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -1110,19 +1110,19 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -1133,19 +1133,19 @@
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -1156,19 +1156,19 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -1179,19 +1179,19 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -1202,19 +1202,19 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -1225,19 +1225,19 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -1248,19 +1248,19 @@
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -1271,19 +1271,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -1294,19 +1294,19 @@
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
